--- a/artfynd/A 57553-2021 artfynd.xlsx
+++ b/artfynd/A 57553-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117901045</v>
+        <v>117901046</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>90464</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117901043</v>
+        <v>117901044</v>
       </c>
       <c r="B3" t="n">
-        <v>90519</v>
+        <v>97836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611240</v>
+        <v>611261</v>
       </c>
       <c r="R3" t="n">
-        <v>6961818</v>
+        <v>6961815</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117901044</v>
+        <v>117901043</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>90519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611261</v>
+        <v>611240</v>
       </c>
       <c r="R4" t="n">
-        <v>6961815</v>
+        <v>6961818</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117901046</v>
+        <v>117901045</v>
       </c>
       <c r="B5" t="n">
-        <v>90464</v>
+        <v>78480</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 57553-2021 artfynd.xlsx
+++ b/artfynd/A 57553-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117901046</v>
+        <v>117901044</v>
       </c>
       <c r="B2" t="n">
-        <v>90464</v>
+        <v>97838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611323</v>
+        <v>611261</v>
       </c>
       <c r="R2" t="n">
-        <v>6961789</v>
+        <v>6961815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117901044</v>
+        <v>117901043</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>90521</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611261</v>
+        <v>611240</v>
       </c>
       <c r="R3" t="n">
-        <v>6961815</v>
+        <v>6961818</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117901043</v>
+        <v>117901046</v>
       </c>
       <c r="B4" t="n">
-        <v>90519</v>
+        <v>90466</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611240</v>
+        <v>611323</v>
       </c>
       <c r="R4" t="n">
-        <v>6961818</v>
+        <v>6961789</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>117901045</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 57553-2021 artfynd.xlsx
+++ b/artfynd/A 57553-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117901046</v>
+        <v>117901043</v>
       </c>
       <c r="B2" t="n">
-        <v>90468</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611323</v>
+        <v>611240</v>
       </c>
       <c r="R2" t="n">
-        <v>6961789</v>
+        <v>6961818</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117901045</v>
+        <v>117901046</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117901043</v>
+        <v>117901045</v>
       </c>
       <c r="B4" t="n">
-        <v>90523</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611240</v>
+        <v>611323</v>
       </c>
       <c r="R4" t="n">
-        <v>6961818</v>
+        <v>6961789</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +969,7 @@
         <v>117901044</v>
       </c>
       <c r="B5" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57553-2021 artfynd.xlsx
+++ b/artfynd/A 57553-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901043</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901046</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901045</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117901044</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>